--- a/data/trans_dic/P2A_enfcro_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,67; 67,83</t>
+          <t>47,85; 69,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,13; 71,92</t>
+          <t>49,67; 71,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43,47; 68,17</t>
+          <t>44,03; 68,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83,44; 96,32</t>
+          <t>81,67; 96,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>53,28; 74,61</t>
+          <t>51,86; 73,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,28; 72,02</t>
+          <t>51,4; 71,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,09; 61,29</t>
+          <t>38,12; 60,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>80,42; 94,08</t>
+          <t>81,07; 94,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,8; 68,35</t>
+          <t>51,99; 67,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54,66; 69,38</t>
+          <t>53,56; 68,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43,79; 60,5</t>
+          <t>43,18; 60,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,48; 94,14</t>
+          <t>83,94; 93,97</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,4; 43,21</t>
+          <t>34,61; 43,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,26; 50,98</t>
+          <t>41,13; 50,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,36; 45,85</t>
+          <t>37,74; 46,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92,14; 95,88</t>
+          <t>91,83; 95,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,06; 46,41</t>
+          <t>37,41; 46,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,54; 52,34</t>
+          <t>43,27; 52,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,22; 45,11</t>
+          <t>36,98; 44,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>91,75; 95,76</t>
+          <t>91,5; 95,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,28; 43,53</t>
+          <t>37,59; 43,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,06; 50,39</t>
+          <t>43,66; 50,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38,37; 44,52</t>
+          <t>38,11; 44,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>92,54; 95,49</t>
+          <t>92,69; 95,51</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,71; 41,59</t>
+          <t>28,7; 42,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,56; 48,95</t>
+          <t>34,27; 49,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,36; 46,7</t>
+          <t>33,06; 47,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>98,56; 100,0</t>
+          <t>98,48; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,57; 44,42</t>
+          <t>29,56; 44,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,11; 49,4</t>
+          <t>35,15; 48,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,21; 45,4</t>
+          <t>32,1; 45,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>96,69; 99,63</t>
+          <t>96,99; 99,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,4; 40,57</t>
+          <t>31,07; 40,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36,82; 47,09</t>
+          <t>36,74; 47,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,64; 44,11</t>
+          <t>34,57; 44,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>97,98; 99,62</t>
+          <t>97,96; 99,7</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,09; 43,32</t>
+          <t>36,33; 43,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,08; 50,23</t>
+          <t>43,1; 50,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,94; 45,67</t>
+          <t>39,05; 46,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93,55; 96,47</t>
+          <t>93,53; 96,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,43; 46,47</t>
+          <t>39,46; 46,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,3; 51,32</t>
+          <t>44,4; 51,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,88; 44,67</t>
+          <t>37,91; 44,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>93,08; 96,1</t>
+          <t>92,96; 96,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,83; 43,63</t>
+          <t>38,91; 43,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44,8; 49,78</t>
+          <t>44,72; 50,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39,31; 44,27</t>
+          <t>39,18; 44,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,83; 95,89</t>
+          <t>93,81; 95,87</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>32548</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>34242</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>22761</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>49848</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>32599</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>38355</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>25228</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>55138</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>65146</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>72597</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>47988</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>104985</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>27015; 39025</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>27556; 39637</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17893; 27690</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>44656; 52749</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>26643; 37573</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>31912; 44269</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>19531; 30811</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>50264; 58440</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>56061; 72820</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>62977; 81064</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>39674; 55175</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>97938; 109649</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1222</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>120084</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>139588</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>145643</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>433402</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>148084</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>163352</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>155436</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>486020</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>268168</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>302940</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>301079</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>919421</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>107405; 133462</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>125310; 153606</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>131624; 160767</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>422890; 442064</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>132278; 162964</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>147023; 177424</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>140461; 170692</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>472691; 494543</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>249576; 289936</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>281378; 322941</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>277646; 322709</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>905655; 933228</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>47514</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>48563</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>54269</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>149001</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>45550</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>57366</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>53955</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>181012</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>93064</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>105929</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>108224</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>330013</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>39195; 57496</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>40033; 57331</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>44973; 64010</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>147274; 149551</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>36524; 54742</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>48124; 66797</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>44917; 63175</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>177829; 182716</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>80823; 105365</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>93223; 119494</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>95398; 123207</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>326101; 331905</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>892</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1817</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>200145</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>222394</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>222674</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>632250</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>226233</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>259073</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>234618</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>722169</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>426378</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>481467</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>457292</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1354419</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>182877; 216941</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205564; 239769</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205187; 245939</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>621760; 641313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>208567; 243856</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>239227; 276099</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>216460; 254440</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>708305; 732249</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>401501; 451997</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>454290; 509320</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>429534; 483422</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1338446; 1367718</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_enfcro_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>47,85; 69,12</t>
+          <t>46,81; 67,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,67; 71,44</t>
+          <t>50,13; 71,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,03; 68,13</t>
+          <t>42,86; 67,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81,67; 96,47</t>
+          <t>82,89; 96,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,86; 73,14</t>
+          <t>52,5; 74,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,4; 71,3</t>
+          <t>51,07; 71,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,12; 60,13</t>
+          <t>37,23; 60,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>81,07; 94,25</t>
+          <t>81,23; 94,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>51,99; 67,53</t>
+          <t>53,07; 68,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53,56; 68,95</t>
+          <t>54,23; 68,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43,18; 60,05</t>
+          <t>43,8; 60,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,94; 93,97</t>
+          <t>83,61; 93,74</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,61; 43,01</t>
+          <t>34,54; 43,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,13; 50,42</t>
+          <t>40,76; 50,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,74; 46,1</t>
+          <t>37,72; 46,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91,83; 95,99</t>
+          <t>91,93; 95,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,41; 46,08</t>
+          <t>37,72; 46,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,27; 52,22</t>
+          <t>43,19; 52,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,98; 44,93</t>
+          <t>36,66; 45,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>91,5; 95,73</t>
+          <t>91,64; 96,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,59; 43,67</t>
+          <t>37,56; 43,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43,66; 50,11</t>
+          <t>43,77; 50,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38,11; 44,29</t>
+          <t>38,52; 44,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>92,69; 95,51</t>
+          <t>92,75; 95,49</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,7; 42,1</t>
+          <t>28,49; 42,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,27; 49,07</t>
+          <t>34,09; 49,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,06; 47,06</t>
+          <t>33,51; 47,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>98,48; 100,0</t>
+          <t>98,47; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,56; 44,31</t>
+          <t>29,52; 43,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,15; 48,79</t>
+          <t>34,59; 49,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,1; 45,15</t>
+          <t>31,85; 45,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>96,99; 99,65</t>
+          <t>96,87; 99,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,07; 40,51</t>
+          <t>30,91; 40,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36,74; 47,1</t>
+          <t>36,86; 47,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,57; 44,65</t>
+          <t>34,82; 43,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>97,96; 99,7</t>
+          <t>97,99; 99,68</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,33; 43,1</t>
+          <t>35,99; 43,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,1; 50,27</t>
+          <t>42,91; 50,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,05; 46,81</t>
+          <t>39,25; 45,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93,53; 96,48</t>
+          <t>93,62; 96,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,46; 46,14</t>
+          <t>39,5; 46,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,4; 51,25</t>
+          <t>44,59; 51,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,91; 44,56</t>
+          <t>37,51; 44,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>92,96; 96,1</t>
+          <t>93,06; 96,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,91; 43,8</t>
+          <t>38,72; 43,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44,72; 50,14</t>
+          <t>44,74; 49,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39,18; 44,09</t>
+          <t>39,26; 44,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,81; 95,87</t>
+          <t>93,71; 95,95</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27015; 39025</t>
+          <t>26430; 38050</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27556; 39637</t>
+          <t>27813; 39678</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17893; 27690</t>
+          <t>17417; 27451</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44656; 52749</t>
+          <t>45324; 52820</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26643; 37573</t>
+          <t>26971; 38015</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31912; 44269</t>
+          <t>31712; 44313</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19531; 30811</t>
+          <t>19076; 30930</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50264; 58440</t>
+          <t>50364; 58565</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>56061; 72820</t>
+          <t>57226; 73504</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62977; 81064</t>
+          <t>63765; 80775</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39674; 55175</t>
+          <t>40242; 55283</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>97938; 109649</t>
+          <t>97555; 109377</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>107405; 133462</t>
+          <t>107170; 134637</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>125310; 153606</t>
+          <t>124178; 153156</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>131624; 160767</t>
+          <t>131534; 160631</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>422890; 442064</t>
+          <t>423368; 442001</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>132278; 162964</t>
+          <t>133390; 164486</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>147023; 177424</t>
+          <t>146757; 178494</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>140461; 170692</t>
+          <t>139244; 172302</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>472691; 494543</t>
+          <t>473407; 496160</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>249576; 289936</t>
+          <t>249363; 288152</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>281378; 322941</t>
+          <t>282050; 324515</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>277646; 322709</t>
+          <t>280669; 322461</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>905655; 933228</t>
+          <t>906297; 933095</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39195; 57496</t>
+          <t>38913; 57653</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>40033; 57331</t>
+          <t>39825; 57322</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44973; 64010</t>
+          <t>45583; 64085</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>147274; 149551</t>
+          <t>147261; 149551</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36524; 54742</t>
+          <t>36464; 53717</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48124; 66797</t>
+          <t>47353; 67920</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44917; 63175</t>
+          <t>44562; 64220</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>177829; 182716</t>
+          <t>177603; 182722</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>80823; 105365</t>
+          <t>80405; 105773</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>93223; 119494</t>
+          <t>93515; 119290</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95398; 123207</t>
+          <t>96091; 121355</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>326101; 331905</t>
+          <t>326212; 331843</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>182877; 216941</t>
+          <t>181145; 217000</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>205564; 239769</t>
+          <t>204644; 239956</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>205187; 245939</t>
+          <t>206228; 241106</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>621760; 641313</t>
+          <t>622325; 641289</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>208567; 243856</t>
+          <t>208778; 245146</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>239227; 276099</t>
+          <t>240217; 278303</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>216460; 254440</t>
+          <t>214222; 253416</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>708305; 732249</t>
+          <t>709120; 732502</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>401501; 451997</t>
+          <t>399580; 453282</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>454290; 509320</t>
+          <t>454476; 506927</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>429534; 483422</t>
+          <t>430455; 483498</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1338446; 1367718</t>
+          <t>1336962; 1368909</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_enfcro_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>63,46%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>61,77%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>49,24%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>88,77%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>57,65%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>61,71%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>56,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>91,17%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>63,46%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>61,77%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>49,24%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,27%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>46,81; 67,39</t>
+          <t>53,28; 74,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,13; 71,51</t>
+          <t>50,28; 72,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42,86; 67,55</t>
+          <t>38,09; 61,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82,89; 96,6</t>
+          <t>80,44; 94,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,5; 74,0</t>
+          <t>45,67; 67,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,07; 71,37</t>
+          <t>50,13; 71,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,23; 60,37</t>
+          <t>43,47; 68,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>81,23; 94,45</t>
+          <t>81,51; 95,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,07; 68,16</t>
+          <t>52,8; 68,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54,23; 68,7</t>
+          <t>54,66; 69,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43,8; 60,17</t>
+          <t>43,79; 60,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,61; 93,74</t>
+          <t>82,93; 93,41</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>41,87%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>48,07%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>40,92%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>94,1%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>38,7%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>45,82%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>41,76%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>94,11%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>41,87%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>48,07%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>40,92%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,54; 43,39</t>
+          <t>38,06; 46,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,76; 50,27</t>
+          <t>43,54; 52,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,72; 46,06</t>
+          <t>37,22; 45,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91,93; 95,98</t>
+          <t>91,63; 95,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,72; 46,51</t>
+          <t>34,4; 43,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,19; 52,53</t>
+          <t>41,26; 50,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,66; 45,36</t>
+          <t>37,36; 45,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>91,64; 96,04</t>
+          <t>91,82; 95,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,56; 43,4</t>
+          <t>37,28; 43,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43,77; 50,36</t>
+          <t>44,06; 50,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38,52; 44,26</t>
+          <t>38,37; 44,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>92,75; 95,49</t>
+          <t>92,36; 95,35</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>36,87%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>41,9%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>38,56%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>34,79%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>41,57%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>39,9%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>36,87%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>41,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,56%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,49; 42,21</t>
+          <t>29,57; 44,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,09; 49,07</t>
+          <t>35,11; 49,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,51; 47,11</t>
+          <t>32,21; 45,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>98,47; 100,0</t>
+          <t>96,42; 99,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,52; 43,48</t>
+          <t>27,71; 41,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,59; 49,61</t>
+          <t>34,56; 48,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,85; 45,89</t>
+          <t>33,36; 46,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>96,87; 99,66</t>
+          <t>98,53; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,91; 40,66</t>
+          <t>31,4; 40,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36,86; 47,02</t>
+          <t>36,82; 47,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,82; 43,98</t>
+          <t>34,64; 44,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>97,99; 99,68</t>
+          <t>98,01; 99,61</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>48,08%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>41,09%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>94,77%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>39,76%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>46,63%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>42,38%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>95,11%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>42,8%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>48,08%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>41,09%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,99; 43,11</t>
+          <t>39,43; 46,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,91; 50,31</t>
+          <t>44,3; 51,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,25; 45,89</t>
+          <t>37,88; 44,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93,62; 96,47</t>
+          <t>93,03; 96,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,5; 46,38</t>
+          <t>36,09; 43,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,59; 51,65</t>
+          <t>43,08; 50,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,51; 44,38</t>
+          <t>38,94; 45,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>93,06; 96,13</t>
+          <t>93,14; 96,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,72; 43,93</t>
+          <t>38,83; 43,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44,74; 49,91</t>
+          <t>44,8; 49,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39,26; 44,1</t>
+          <t>39,31; 44,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,71; 95,95</t>
+          <t>93,59; 95,77</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>61</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32599</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38355</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25228</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>50362</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>32548</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>34242</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>22761</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>49848</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>32599</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>38355</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>25228</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55138</t>
+          <t>42028</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>104985</t>
+          <t>92390</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26430; 38050</t>
+          <t>27369; 38329</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27813; 39678</t>
+          <t>31218; 44717</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17417; 27451</t>
+          <t>19517; 31404</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45324; 52820</t>
+          <t>45634; 53445</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26971; 38015</t>
+          <t>25789; 38297</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31712; 44313</t>
+          <t>27812; 39905</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19076; 30930</t>
+          <t>17668; 27704</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50364; 58565</t>
+          <t>38115; 44695</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>57226; 73504</t>
+          <t>56941; 73708</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63765; 80775</t>
+          <t>64264; 81574</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40242; 55283</t>
+          <t>40236; 55589</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>97555; 109377</t>
+          <t>85823; 96670</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>603</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>148084</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>163352</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>155436</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>447597</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>120084</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>139588</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>145643</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>433402</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>148084</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>163352</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>155436</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>486020</t>
+          <t>405661</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>919421</t>
+          <t>853258</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>107170; 134637</t>
+          <t>134609; 164133</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>124178; 153156</t>
+          <t>147934; 177836</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>131534; 160631</t>
+          <t>141402; 171342</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423368; 442001</t>
+          <t>435845; 455529</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>133390; 164486</t>
+          <t>106734; 134089</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>146757; 178494</t>
+          <t>125707; 155318</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>139244; 172302</t>
+          <t>130299; 159876</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>473407; 496160</t>
+          <t>397056; 413827</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>249363; 288152</t>
+          <t>247497; 289004</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>282050; 324515</t>
+          <t>283912; 324760</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>280669; 322461</t>
+          <t>279528; 324381</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>906297; 933095</t>
+          <t>838764; 865940</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>228</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>45550</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>57366</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>53955</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>166238</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>47514</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>48563</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>54269</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>149001</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>45550</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>57366</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>53955</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>181012</t>
+          <t>149293</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>330013</t>
+          <t>315531</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>38913; 57653</t>
+          <t>36526; 54883</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39825; 57322</t>
+          <t>48063; 67625</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45583; 64085</t>
+          <t>45076; 63523</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>147261; 149551</t>
+          <t>162387; 167705</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36464; 53717</t>
+          <t>37852; 56810</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47353; 67920</t>
+          <t>40376; 57187</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44562; 64220</t>
+          <t>45385; 63518</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>177603; 182722</t>
+          <t>147775; 149976</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>80405; 105773</t>
+          <t>81669; 105529</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>93515; 119290</t>
+          <t>93419; 119487</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>96091; 121355</t>
+          <t>95589; 121723</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>326212; 331843</t>
+          <t>312051; 317149</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>330</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>892</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>226233</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>259073</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>234618</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>664197</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>200145</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>222394</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>222674</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>632250</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>226233</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>259073</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>234618</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>722169</t>
+          <t>596982</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1354419</t>
+          <t>1261179</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>181145; 217000</t>
+          <t>208384; 245623</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>204644; 239956</t>
+          <t>238688; 276489</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>206228; 241106</t>
+          <t>216293; 255101</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>622325; 641289</t>
+          <t>651951; 673502</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>208778; 245146</t>
+          <t>181684; 218077</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>240217; 278303</t>
+          <t>205485; 239569</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>214222; 253416</t>
+          <t>204609; 239933</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>709120; 732502</t>
+          <t>586050; 605882</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>399580; 453282</t>
+          <t>400649; 450187</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>454476; 506927</t>
+          <t>455074; 505661</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>430455; 483498</t>
+          <t>431014; 485340</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1336962; 1368909</t>
+          <t>1244765; 1273714</t>
         </is>
       </c>
     </row>
